--- a/elenco_ndu.xlsx
+++ b/elenco_ndu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\leand\Pictures\Academia Demônios\Escalações_Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2FED8F-8956-4999-A6C2-76EDCE986FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724C2FCA-B175-4E46-AB00-43C569D763E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{F41566AD-B607-4AE4-89B4-162702A84AD2}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11332" xr2:uid="{F41566AD-B607-4AE4-89B4-162702A84AD2}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="95">
   <si>
     <t xml:space="preserve">Alfredo Camera de Menezes </t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>Nome Completo</t>
+  </si>
+  <si>
+    <t>Telefone</t>
   </si>
 </sst>
 </file>
@@ -682,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33B0CFA5-553C-4F0F-B831-E8CF40A0439F}">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.9296875" customWidth="1"/>
@@ -692,7 +695,7 @@
     <col min="5" max="5" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -714,8 +717,11 @@
       <c r="H1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -723,7 +729,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -731,7 +737,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
@@ -739,7 +745,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,7 +753,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
@@ -755,7 +761,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -769,7 +775,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
@@ -777,7 +783,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
@@ -785,7 +791,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -799,7 +805,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
@@ -807,7 +813,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
@@ -815,7 +821,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>88</v>
       </c>
@@ -829,7 +835,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -843,7 +849,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -857,7 +863,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>56</v>
       </c>
